--- a/data/Vietanm_electricity_statistics.xlsx
+++ b/data/Vietanm_electricity_statistics.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28129"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\mye500\projects\Map2Grid\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AF54CEA-49D4-4D4B-A554-70BBB01A26FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD427A85-F2E6-47C1-9F38-063F4BF503AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-1526" yWindow="10183" windowWidth="19543" windowHeight="12377" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-1526" yWindow="10183" windowWidth="19543" windowHeight="12377" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Installed_capacity" sheetId="1" r:id="rId1"/>
@@ -3388,7 +3388,7 @@
         <v>66</v>
       </c>
       <c r="C18" s="12">
-        <f>I18/$I$80*$C$80</f>
+        <f t="shared" ref="C18:C40" si="0">I18/$I$80*$C$80</f>
         <v>17667.596425966785</v>
       </c>
       <c r="D18" s="4">
@@ -3418,7 +3418,7 @@
         <v>67</v>
       </c>
       <c r="C19" s="12">
-        <f>I19/$I$80*$C$80</f>
+        <f t="shared" si="0"/>
         <v>4255.0298829907761</v>
       </c>
       <c r="D19" s="4">
@@ -3448,7 +3448,7 @@
         <v>68</v>
       </c>
       <c r="C20" s="12">
-        <f>I20/$I$80*$C$80</f>
+        <f t="shared" si="0"/>
         <v>241.69078558094094</v>
       </c>
       <c r="D20" s="4">
@@ -3478,7 +3478,7 @@
         <v>69</v>
       </c>
       <c r="C21" s="12">
-        <f>I21/$I$80*$C$80</f>
+        <f t="shared" si="0"/>
         <v>8423.5599058788994</v>
       </c>
       <c r="D21" s="4">
@@ -3508,7 +3508,7 @@
         <v>70</v>
       </c>
       <c r="C22" s="12">
-        <f>I22/$I$80*$C$80</f>
+        <f t="shared" si="0"/>
         <v>4117.6477522395044</v>
       </c>
       <c r="D22" s="4">
@@ -3538,7 +3538,7 @@
         <v>71</v>
       </c>
       <c r="C23" s="12">
-        <f>I23/$I$80*$C$80</f>
+        <f t="shared" si="0"/>
         <v>4509.4412362338717</v>
       </c>
       <c r="D23" s="4">
@@ -3568,7 +3568,7 @@
         <v>72</v>
       </c>
       <c r="C24" s="12">
-        <f>I24/$I$80*$C$80</f>
+        <f t="shared" si="0"/>
         <v>6093.1519101721424</v>
       </c>
       <c r="D24" s="4">
@@ -3598,7 +3598,7 @@
         <v>73</v>
       </c>
       <c r="C25" s="12">
-        <f>I25/$I$80*$C$80</f>
+        <f t="shared" si="0"/>
         <v>3788.1850497896953</v>
       </c>
       <c r="D25" s="4">
@@ -3628,7 +3628,7 @@
         <v>74</v>
       </c>
       <c r="C26" s="12">
-        <f>I26/$I$80*$C$80</f>
+        <f t="shared" si="0"/>
         <v>454.12426553892584</v>
       </c>
       <c r="D26" s="4">
@@ -3658,7 +3658,7 @@
         <v>75</v>
       </c>
       <c r="C27" s="12">
-        <f>I27/$I$80*$C$80</f>
+        <f t="shared" si="0"/>
         <v>231.51433145121709</v>
       </c>
       <c r="D27" s="4">
@@ -3688,7 +3688,7 @@
         <v>76</v>
       </c>
       <c r="C28" s="12">
-        <f>I28/$I$80*$C$80</f>
+        <f t="shared" si="0"/>
         <v>2823.9660209983626</v>
       </c>
       <c r="D28" s="4">
@@ -3718,7 +3718,7 @@
         <v>77</v>
       </c>
       <c r="C29" s="12">
-        <f>I29/$I$80*$C$80</f>
+        <f t="shared" si="0"/>
         <v>9717.2416371200416</v>
       </c>
       <c r="D29" s="4">
@@ -3748,7 +3748,7 @@
         <v>78</v>
       </c>
       <c r="C30" s="12">
-        <f>I30/$I$80*$C$80</f>
+        <f t="shared" si="0"/>
         <v>14496.358907791593</v>
       </c>
       <c r="D30" s="4">
@@ -3778,7 +3778,7 @@
         <v>79</v>
       </c>
       <c r="C31" s="12">
-        <f>I31/$I$80*$C$80</f>
+        <f t="shared" si="0"/>
         <v>10902.798543232866</v>
       </c>
       <c r="D31" s="4">
@@ -3808,7 +3808,7 @@
         <v>80</v>
       </c>
       <c r="C32" s="12">
-        <f>I32/$I$80*$C$80</f>
+        <f t="shared" si="0"/>
         <v>11009.651311594967</v>
       </c>
       <c r="D32" s="4">
@@ -3838,7 +3838,7 @@
         <v>81</v>
       </c>
       <c r="C33" s="12">
-        <f>I33/$I$80*$C$80</f>
+        <f t="shared" si="0"/>
         <v>2077.2686992298763</v>
       </c>
       <c r="D33" s="4">
@@ -3868,7 +3868,7 @@
         <v>82</v>
       </c>
       <c r="C34" s="12">
-        <f>I34/$I$80*$C$80</f>
+        <f t="shared" si="0"/>
         <v>3325.1563868872609</v>
       </c>
       <c r="D34" s="4">
@@ -3898,7 +3898,7 @@
         <v>83</v>
       </c>
       <c r="C35" s="12">
-        <f>I35/$I$80*$C$80</f>
+        <f t="shared" si="0"/>
         <v>8474.4421765275183</v>
       </c>
       <c r="D35" s="4">
@@ -3928,7 +3928,7 @@
         <v>84</v>
       </c>
       <c r="C36" s="12">
-        <f>I36/$I$80*$C$80</f>
+        <f t="shared" si="0"/>
         <v>1152.4834301912235</v>
       </c>
       <c r="D36" s="4">
@@ -3958,7 +3958,7 @@
         <v>85</v>
       </c>
       <c r="C37" s="12">
-        <f>I37/$I$80*$C$80</f>
+        <f t="shared" si="0"/>
         <v>465.57277643486515</v>
       </c>
       <c r="D37" s="4">
@@ -3988,7 +3988,7 @@
         <v>86</v>
       </c>
       <c r="C38" s="12">
-        <f>I38/$I$80*$C$80</f>
+        <f t="shared" si="0"/>
         <v>962.94697202511725</v>
       </c>
       <c r="D38" s="4">
@@ -4018,7 +4018,7 @@
         <v>87</v>
       </c>
       <c r="C39" s="12">
-        <f>I39/$I$80*$C$80</f>
+        <f t="shared" si="0"/>
         <v>465.57277643486515</v>
       </c>
       <c r="D39" s="4">
@@ -4048,7 +4048,7 @@
         <v>88</v>
       </c>
       <c r="C40" s="12">
-        <f>I40/$I$80*$C$80</f>
+        <f t="shared" si="0"/>
         <v>933.68966640216138</v>
       </c>
       <c r="D40" s="4">
@@ -4413,7 +4413,7 @@
         <v>102</v>
       </c>
       <c r="C55" s="16">
-        <f>I55/$I$80*$C$80</f>
+        <f t="shared" ref="C55:C60" si="1">I55/$I$80*$C$80</f>
         <v>2252.8125329676127</v>
       </c>
       <c r="D55" s="4">
@@ -4443,7 +4443,7 @@
         <v>103</v>
       </c>
       <c r="C56" s="16">
-        <f>I56/$I$80*$C$80</f>
+        <f t="shared" si="1"/>
         <v>628.39604251044636</v>
       </c>
       <c r="D56" s="4">
@@ -4473,7 +4473,7 @@
         <v>104</v>
       </c>
       <c r="C57" s="16">
-        <f>I57/$I$80*$C$80</f>
+        <f t="shared" si="1"/>
         <v>480.83745762945091</v>
       </c>
       <c r="D57" s="4">
@@ -4503,7 +4503,7 @@
         <v>105</v>
       </c>
       <c r="C58" s="16">
-        <f>I58/$I$80*$C$80</f>
+        <f t="shared" si="1"/>
         <v>93061.128902791985</v>
       </c>
       <c r="D58" s="6">
@@ -4533,7 +4533,7 @@
         <v>106</v>
       </c>
       <c r="C59" s="16">
-        <f>I59/$I$80*$C$80</f>
+        <f t="shared" si="1"/>
         <v>2447.4372181985809</v>
       </c>
       <c r="D59">
@@ -4563,7 +4563,7 @@
         <v>107</v>
       </c>
       <c r="C60" s="16">
-        <f>I60/$I$80*$C$80</f>
+        <f t="shared" si="1"/>
         <v>2893.9291431402139</v>
       </c>
       <c r="D60">

--- a/data/Vietanm_electricity_statistics.xlsx
+++ b/data/Vietanm_electricity_statistics.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28227"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\mye500\projects\Map2Grid\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD427A85-F2E6-47C1-9F38-063F4BF503AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F939AF1-9487-4E44-A8D6-0E2DA8B21B6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-1526" yWindow="10183" windowWidth="19543" windowHeight="12377" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="19543" windowHeight="12377" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Installed_capacity" sheetId="1" r:id="rId1"/>
@@ -947,13 +947,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="27.44140625" customWidth="1"/>
-    <col min="2" max="2" width="18.21875" style="12" customWidth="1"/>
+    <col min="1" max="1" width="27.453125" customWidth="1"/>
+    <col min="2" max="2" width="18.1796875" style="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" s="13" t="s">
         <v>144</v>
       </c>
@@ -979,7 +979,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="I2" s="12"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -1032,7 +1032,7 @@
         <v>22077</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -1058,7 +1058,7 @@
         <v>1579</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -1084,7 +1084,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -1110,7 +1110,7 @@
         <v>7422</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" s="14" t="s">
         <v>146</v>
       </c>
@@ -1136,7 +1136,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" s="14" t="s">
         <v>15</v>
       </c>
@@ -1162,7 +1162,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" s="14" t="s">
         <v>16</v>
       </c>
@@ -1179,7 +1179,7 @@
         <v>8852</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -1202,7 +1202,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" s="6" t="s">
         <v>18</v>
       </c>
@@ -1225,7 +1225,7 @@
         <v>62248</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" s="6" t="s">
         <v>19</v>
       </c>
@@ -1248,7 +1248,7 @@
         <v>38617</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>20</v>
       </c>
@@ -1279,13 +1279,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64A85155-C431-48CF-8846-E6F819EB5409}">
   <dimension ref="A1:N25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="57.21875" customWidth="1"/>
-    <col min="2" max="2" width="21.109375" customWidth="1"/>
+    <col min="1" max="1" width="57.1796875" customWidth="1"/>
+    <col min="2" max="2" width="21.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" s="13" t="s">
         <v>145</v>
       </c>
@@ -1311,7 +1311,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>21</v>
       </c>
@@ -1337,7 +1337,7 @@
         <v>72892</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>22</v>
       </c>
@@ -1363,7 +1363,7 @@
         <v>123177</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>23</v>
       </c>
@@ -1389,7 +1389,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>24</v>
       </c>
@@ -1415,7 +1415,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>27</v>
       </c>
@@ -1441,7 +1441,7 @@
         <v>34802</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7" s="14" t="s">
         <v>146</v>
       </c>
@@ -1467,7 +1467,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8" s="14" t="s">
         <v>15</v>
       </c>
@@ -1493,7 +1493,7 @@
         <v>982</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9" s="14" t="s">
         <v>16</v>
       </c>
@@ -1510,7 +1510,7 @@
         <v>9575</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -1533,7 +1533,7 @@
         <v>3067</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>34</v>
       </c>
@@ -1556,7 +1556,7 @@
         <v>1555</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A12" s="6" t="s">
         <v>35</v>
       </c>
@@ -1604,13 +1604,13 @@
         <v>245898</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13" s="6" t="s">
         <v>47</v>
       </c>
       <c r="B13" s="6"/>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>36</v>
       </c>
@@ -1633,7 +1633,7 @@
         <v>7388</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>37</v>
       </c>
@@ -1656,7 +1656,7 @@
         <v>117675</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>38</v>
       </c>
@@ -1679,7 +1679,7 @@
         <v>10352</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>39</v>
       </c>
@@ -1702,7 +1702,7 @@
         <v>73158</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>40</v>
       </c>
@@ -1725,7 +1725,7 @@
         <v>8973</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A19" s="6" t="s">
         <v>18</v>
       </c>
@@ -1773,7 +1773,7 @@
         <v>217546</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>41</v>
       </c>
@@ -1796,13 +1796,13 @@
         <v>6.42</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A21" s="6" t="s">
         <v>32</v>
       </c>
       <c r="B21" s="6"/>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>42</v>
       </c>
@@ -1825,7 +1825,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>43</v>
       </c>
@@ -1848,7 +1848,7 @@
         <v>3.11</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>44</v>
       </c>
@@ -1871,7 +1871,7 @@
         <v>0.77</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>45</v>
       </c>
@@ -1902,12 +1902,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA7F0D24-CCF2-4A85-8875-2CE1DB07434F}">
   <dimension ref="A1:G47"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="31.33203125" customWidth="1"/>
+    <col min="1" max="1" width="31.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1930,7 +1930,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>30</v>
       </c>
@@ -1941,7 +1941,7 @@
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -1964,7 +1964,7 @@
         <v>20859</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -1987,7 +1987,7 @@
         <v>22077</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -2010,7 +2010,7 @@
         <v>1579</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -2033,7 +2033,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -2056,7 +2056,7 @@
         <v>7422</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="5" t="s">
         <v>12</v>
       </c>
@@ -2079,7 +2079,7 @@
         <v>7398</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="5" t="s">
         <v>11</v>
       </c>
@@ -2102,7 +2102,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -2125,7 +2125,7 @@
         <v>9715</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="5" t="s">
         <v>14</v>
       </c>
@@ -2148,7 +2148,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="5" t="s">
         <v>15</v>
       </c>
@@ -2171,7 +2171,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="5" t="s">
         <v>16</v>
       </c>
@@ -2194,7 +2194,7 @@
         <v>8852</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>17</v>
       </c>
@@ -2217,7 +2217,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" s="6" t="s">
         <v>18</v>
       </c>
@@ -2240,7 +2240,7 @@
         <v>62248</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" s="6" t="s">
         <v>19</v>
       </c>
@@ -2263,7 +2263,7 @@
         <v>38617</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>20</v>
       </c>
@@ -2286,12 +2286,12 @@
         <v>38</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>21</v>
       </c>
@@ -2314,7 +2314,7 @@
         <v>72892</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>22</v>
       </c>
@@ -2337,7 +2337,7 @@
         <v>123177</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>23</v>
       </c>
@@ -2360,7 +2360,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>24</v>
       </c>
@@ -2383,7 +2383,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" s="5" t="s">
         <v>25</v>
       </c>
@@ -2406,7 +2406,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24" s="5" t="s">
         <v>26</v>
       </c>
@@ -2429,7 +2429,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>27</v>
       </c>
@@ -2452,7 +2452,7 @@
         <v>34802</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26" s="5" t="s">
         <v>28</v>
       </c>
@@ -2475,7 +2475,7 @@
         <v>34657</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27" s="5" t="s">
         <v>33</v>
       </c>
@@ -2498,7 +2498,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>13</v>
       </c>
@@ -2521,7 +2521,7 @@
         <v>10897</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29" s="5" t="s">
         <v>14</v>
       </c>
@@ -2544,7 +2544,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30" s="5" t="s">
         <v>15</v>
       </c>
@@ -2567,7 +2567,7 @@
         <v>982</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31" s="5" t="s">
         <v>16</v>
       </c>
@@ -2590,7 +2590,7 @@
         <v>9575</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>17</v>
       </c>
@@ -2613,7 +2613,7 @@
         <v>3067</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>34</v>
       </c>
@@ -2636,7 +2636,7 @@
         <v>1555</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34" s="6" t="s">
         <v>35</v>
       </c>
@@ -2659,12 +2659,12 @@
         <v>245898</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35" s="6" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>36</v>
       </c>
@@ -2687,7 +2687,7 @@
         <v>7388</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>37</v>
       </c>
@@ -2710,7 +2710,7 @@
         <v>117675</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>38</v>
       </c>
@@ -2733,7 +2733,7 @@
         <v>10352</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>39</v>
       </c>
@@ -2756,7 +2756,7 @@
         <v>73158</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>40</v>
       </c>
@@ -2779,7 +2779,7 @@
         <v>8973</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41" s="6" t="s">
         <v>18</v>
       </c>
@@ -2802,7 +2802,7 @@
         <v>217546</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>41</v>
       </c>
@@ -2825,12 +2825,12 @@
         <v>6.42</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A43" s="6" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>42</v>
       </c>
@@ -2853,7 +2853,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>43</v>
       </c>
@@ -2876,7 +2876,7 @@
         <v>3.11</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>44</v>
       </c>
@@ -2899,7 +2899,7 @@
         <v>0.77</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>45</v>
       </c>
@@ -2930,15 +2930,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C13558E2-00A1-4977-A88F-59E267D57995}">
   <dimension ref="A1:I80"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.6640625" style="7" customWidth="1"/>
-    <col min="2" max="2" width="41.33203125" customWidth="1"/>
+    <col min="1" max="1" width="8.6328125" style="7" customWidth="1"/>
+    <col min="2" max="2" width="41.36328125" customWidth="1"/>
     <col min="3" max="3" width="12" style="12" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
         <v>48</v>
       </c>
@@ -2967,7 +2967,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" s="8">
         <v>1000</v>
       </c>
@@ -2997,7 +2997,7 @@
         <v>7388</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" s="7">
         <v>1100</v>
       </c>
@@ -3006,7 +3006,7 @@
       </c>
       <c r="C3" s="16"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" s="10">
         <v>1110</v>
       </c>
@@ -3036,7 +3036,7 @@
         <v>1319</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" s="10">
         <v>1120</v>
       </c>
@@ -3066,7 +3066,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" s="7">
         <v>1200</v>
       </c>
@@ -3096,7 +3096,7 @@
         <v>2573</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" s="7">
         <v>1300</v>
       </c>
@@ -3126,7 +3126,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" s="7">
         <v>1400</v>
       </c>
@@ -3156,7 +3156,7 @@
         <v>2603</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" s="7">
         <v>1500</v>
       </c>
@@ -3183,7 +3183,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" s="8">
         <v>2000</v>
       </c>
@@ -3213,7 +3213,7 @@
         <v>118146</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" s="7">
         <v>2100</v>
       </c>
@@ -3222,7 +3222,7 @@
       </c>
       <c r="C11" s="16"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" s="10">
         <v>2101</v>
       </c>
@@ -3252,7 +3252,7 @@
         <v>1319</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" s="10">
         <v>2102</v>
       </c>
@@ -3282,7 +3282,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" s="10">
         <v>2103</v>
       </c>
@@ -3312,7 +3312,7 @@
         <v>2573</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" s="10">
         <v>2104</v>
       </c>
@@ -3342,7 +3342,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" s="10">
         <v>2105</v>
       </c>
@@ -3372,15 +3372,19 @@
         <v>2603</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" s="7">
         <v>2200</v>
       </c>
       <c r="B17" s="12" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="C17" s="12">
+        <f>SUM(C18:C40)</f>
+        <v>116589.09085071349</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" s="10">
         <v>2201</v>
       </c>
@@ -3410,7 +3414,7 @@
         <v>13889</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" s="10">
         <v>2202</v>
       </c>
@@ -3440,7 +3444,7 @@
         <v>3345</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20" s="10">
         <v>2203</v>
       </c>
@@ -3470,7 +3474,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21" s="10">
         <v>2204</v>
       </c>
@@ -3500,7 +3504,7 @@
         <v>6622</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22" s="10">
         <v>2205</v>
       </c>
@@ -3530,7 +3534,7 @@
         <v>3237</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23" s="10">
         <v>2206</v>
       </c>
@@ -3560,7 +3564,7 @@
         <v>3545</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24" s="10">
         <v>2207</v>
       </c>
@@ -3590,7 +3594,7 @@
         <v>4790</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A25" s="10">
         <v>2208</v>
       </c>
@@ -3620,7 +3624,7 @@
         <v>2978</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A26" s="10">
         <v>2209</v>
       </c>
@@ -3650,7 +3654,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A27" s="10">
         <v>2210</v>
       </c>
@@ -3680,7 +3684,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A28" s="10">
         <v>2211</v>
       </c>
@@ -3710,7 +3714,7 @@
         <v>2220</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A29" s="10">
         <v>2212</v>
       </c>
@@ -3740,7 +3744,7 @@
         <v>7639</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A30" s="10">
         <v>2213</v>
       </c>
@@ -3770,7 +3774,7 @@
         <v>11396</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A31" s="10">
         <v>2214</v>
       </c>
@@ -3800,7 +3804,7 @@
         <v>8571</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A32" s="10">
         <v>2215</v>
       </c>
@@ -3830,7 +3834,7 @@
         <v>8655</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A33" s="10">
         <v>2216</v>
       </c>
@@ -3860,7 +3864,7 @@
         <v>1633</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A34" s="10">
         <v>2217</v>
       </c>
@@ -3890,7 +3894,7 @@
         <v>2614</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A35" s="10">
         <v>2218</v>
       </c>
@@ -3920,7 +3924,7 @@
         <v>6662</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A36" s="10">
         <v>2219</v>
       </c>
@@ -3950,7 +3954,7 @@
         <v>906</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A37" s="10">
         <v>2220</v>
       </c>
@@ -3980,7 +3984,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A38" s="10">
         <v>2221</v>
       </c>
@@ -4010,7 +4014,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A39" s="10">
         <v>2222</v>
       </c>
@@ -4040,7 +4044,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A40" s="10">
         <v>2223</v>
       </c>
@@ -4070,7 +4074,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A41" s="7">
         <v>2300</v>
       </c>
@@ -4078,7 +4082,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A42" s="10">
         <v>2301</v>
       </c>
@@ -4108,7 +4112,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A43" s="10">
         <v>2302</v>
       </c>
@@ -4138,7 +4142,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A44" s="10">
         <v>2303</v>
       </c>
@@ -4168,7 +4172,7 @@
         <v>1904</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A45" s="7">
         <v>2400</v>
       </c>
@@ -4177,7 +4181,7 @@
       </c>
       <c r="C45" s="16"/>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A46" s="10">
         <v>2410</v>
       </c>
@@ -4207,7 +4211,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A47" s="10">
         <v>2420</v>
       </c>
@@ -4237,7 +4241,7 @@
         <v>2136</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A48" s="10">
         <v>2430</v>
       </c>
@@ -4267,7 +4271,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A49" s="7">
         <v>2500</v>
       </c>
@@ -4297,7 +4301,7 @@
         <v>13476</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A50" s="8">
         <v>3000</v>
       </c>
@@ -4327,7 +4331,7 @@
         <v>10352</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A51" s="7">
         <v>3100</v>
       </c>
@@ -4336,7 +4340,7 @@
       </c>
       <c r="C51" s="16"/>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A52" s="10">
         <v>3101</v>
       </c>
@@ -4366,7 +4370,7 @@
         <v>7375</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A53" s="10">
         <v>3102</v>
       </c>
@@ -4396,7 +4400,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A54" s="7">
         <v>3200</v>
       </c>
@@ -4405,7 +4409,7 @@
       </c>
       <c r="C54" s="16"/>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A55" s="10">
         <v>3210</v>
       </c>
@@ -4435,7 +4439,7 @@
         <v>1771</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A56" s="10">
         <v>3220</v>
       </c>
@@ -4465,7 +4469,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A57" s="10">
         <v>3230</v>
       </c>
@@ -4495,7 +4499,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A58" s="8">
         <v>4000</v>
       </c>
@@ -4525,7 +4529,7 @@
         <v>73158</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A59" s="7">
         <v>4100</v>
       </c>
@@ -4555,7 +4559,7 @@
         <v>1924</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A60" s="7">
         <v>4300</v>
       </c>
@@ -4585,7 +4589,7 @@
         <v>2275</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A61" s="7">
         <v>4400</v>
       </c>
@@ -4594,7 +4598,7 @@
       </c>
       <c r="C61" s="16"/>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A62" s="10">
         <v>4401</v>
       </c>
@@ -4624,7 +4628,7 @@
         <v>50753</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A63" s="10">
         <v>4402</v>
       </c>
@@ -4654,7 +4658,7 @@
         <v>18200</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A64" s="8">
         <v>5000</v>
       </c>
@@ -4684,7 +4688,7 @@
         <v>8973</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A65" s="7">
         <v>5100</v>
       </c>
@@ -4693,7 +4697,7 @@
       </c>
       <c r="C65" s="16"/>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A66" s="10">
         <v>5101</v>
       </c>
@@ -4723,7 +4727,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A67" s="10">
         <v>5102</v>
       </c>
@@ -4753,7 +4757,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A68" s="10">
         <v>5103</v>
       </c>
@@ -4783,7 +4787,7 @@
         <v>1335</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A69" s="10">
         <v>5104</v>
       </c>
@@ -4813,7 +4817,7 @@
         <v>1828</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A70" s="7">
         <v>5200</v>
       </c>
@@ -4843,7 +4847,7 @@
         <v>2297</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A71" s="7">
         <v>5300</v>
       </c>
@@ -4852,7 +4856,7 @@
       </c>
       <c r="C71" s="16"/>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A72" s="10">
         <v>5301</v>
       </c>
@@ -4882,7 +4886,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A73" s="10">
         <v>5302</v>
       </c>
@@ -4912,7 +4916,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A74" s="7">
         <v>5400</v>
       </c>
@@ -4921,7 +4925,7 @@
       </c>
       <c r="C74" s="16"/>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A75" s="10">
         <v>5401</v>
       </c>
@@ -4951,7 +4955,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A76" s="10">
         <v>5402</v>
       </c>
@@ -4981,7 +4985,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A77" s="10">
         <v>5403</v>
       </c>
@@ -5011,7 +5015,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A78" s="10">
         <v>5404</v>
       </c>
@@ -5041,7 +5045,7 @@
         <v>1399</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A79" s="10">
         <v>5500</v>
       </c>
@@ -5071,7 +5075,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B80" s="8" t="s">
         <v>126</v>
       </c>
@@ -5106,12 +5110,12 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB65EAF5-A56E-4270-8472-89080845ECB0}">
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="20.6640625" customWidth="1"/>
+    <col min="1" max="1" width="20.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -5119,7 +5123,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>130</v>
       </c>
@@ -5127,7 +5131,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>131</v>
       </c>
@@ -5135,7 +5139,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>132</v>
       </c>
@@ -5143,7 +5147,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>133</v>
       </c>
@@ -5151,7 +5155,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>134</v>
       </c>

--- a/data/Vietanm_electricity_statistics.xlsx
+++ b/data/Vietanm_electricity_statistics.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\mye500\projects\Map2Grid\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\BETA-IVM-BAZIS\mye500\projects\Map2Grid\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F939AF1-9487-4E44-A8D6-0E2DA8B21B6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59A672C0-2C3C-462F-AD3C-21FF9AF39BA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="19543" windowHeight="12377" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Installed_capacity" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="148">
   <si>
     <t>Items</t>
   </si>
@@ -481,13 +481,16 @@
   </si>
   <si>
     <t>Biomass</t>
+  </si>
+  <si>
+    <t>Unit: GWh</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -546,6 +549,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B050"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -582,7 +592,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -618,8 +628,15 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -648,8 +665,8 @@
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
-        <row r="335108">
-          <cell r="P335108">
+        <row r="16">
+          <cell r="I16">
             <v>277.33</v>
           </cell>
         </row>
@@ -947,13 +964,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I13"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="27.453125" customWidth="1"/>
-    <col min="2" max="2" width="18.1796875" style="12" customWidth="1"/>
+    <col min="1" max="1" width="27.44140625" customWidth="1"/>
+    <col min="2" max="2" width="18.21875" style="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="13" t="s">
         <v>144</v>
       </c>
@@ -979,7 +996,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -1006,7 +1023,7 @@
       </c>
       <c r="I2" s="12"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -1032,7 +1049,7 @@
         <v>22077</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -1058,7 +1075,7 @@
         <v>1579</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -1084,7 +1101,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -1110,7 +1127,7 @@
         <v>7422</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="14" t="s">
         <v>146</v>
       </c>
@@ -1136,7 +1153,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="14" t="s">
         <v>15</v>
       </c>
@@ -1162,7 +1179,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="14" t="s">
         <v>16</v>
       </c>
@@ -1179,7 +1196,7 @@
         <v>8852</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -1202,7 +1219,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
         <v>18</v>
       </c>
@@ -1225,7 +1242,7 @@
         <v>62248</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
         <v>19</v>
       </c>
@@ -1248,7 +1265,7 @@
         <v>38617</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>20</v>
       </c>
@@ -1279,13 +1296,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64A85155-C431-48CF-8846-E6F819EB5409}">
   <dimension ref="A1:N25"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="57.1796875" customWidth="1"/>
-    <col min="2" max="2" width="21.08984375" customWidth="1"/>
+    <col min="1" max="1" width="57.21875" customWidth="1"/>
+    <col min="2" max="2" width="21.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="13" t="s">
         <v>145</v>
       </c>
@@ -1311,7 +1328,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>21</v>
       </c>
@@ -1337,7 +1354,7 @@
         <v>72892</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>22</v>
       </c>
@@ -1363,7 +1380,7 @@
         <v>123177</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>23</v>
       </c>
@@ -1389,7 +1406,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>24</v>
       </c>
@@ -1415,7 +1432,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>27</v>
       </c>
@@ -1441,7 +1458,7 @@
         <v>34802</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" s="14" t="s">
         <v>146</v>
       </c>
@@ -1467,7 +1484,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="14" t="s">
         <v>15</v>
       </c>
@@ -1493,7 +1510,7 @@
         <v>982</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="14" t="s">
         <v>16</v>
       </c>
@@ -1510,7 +1527,7 @@
         <v>9575</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -1533,7 +1550,7 @@
         <v>3067</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>34</v>
       </c>
@@ -1556,7 +1573,7 @@
         <v>1555</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
         <v>35</v>
       </c>
@@ -1604,13 +1621,13 @@
         <v>245898</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
         <v>47</v>
       </c>
       <c r="B13" s="6"/>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>36</v>
       </c>
@@ -1633,7 +1650,7 @@
         <v>7388</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>37</v>
       </c>
@@ -1656,7 +1673,7 @@
         <v>117675</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>38</v>
       </c>
@@ -1679,7 +1696,7 @@
         <v>10352</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>39</v>
       </c>
@@ -1702,7 +1719,7 @@
         <v>73158</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>40</v>
       </c>
@@ -1725,7 +1742,7 @@
         <v>8973</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
         <v>18</v>
       </c>
@@ -1773,7 +1790,7 @@
         <v>217546</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>41</v>
       </c>
@@ -1796,13 +1813,13 @@
         <v>6.42</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
         <v>32</v>
       </c>
       <c r="B21" s="6"/>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>42</v>
       </c>
@@ -1825,7 +1842,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>43</v>
       </c>
@@ -1848,7 +1865,7 @@
         <v>3.11</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>44</v>
       </c>
@@ -1871,7 +1888,7 @@
         <v>0.77</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>45</v>
       </c>
@@ -1902,12 +1919,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA7F0D24-CCF2-4A85-8875-2CE1DB07434F}">
   <dimension ref="A1:G47"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="31.36328125" customWidth="1"/>
+    <col min="1" max="1" width="31.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1930,7 +1947,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>30</v>
       </c>
@@ -1941,7 +1958,7 @@
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -1964,7 +1981,7 @@
         <v>20859</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -1987,7 +2004,7 @@
         <v>22077</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -2010,7 +2027,7 @@
         <v>1579</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -2033,7 +2050,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -2056,7 +2073,7 @@
         <v>7422</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>12</v>
       </c>
@@ -2079,7 +2096,7 @@
         <v>7398</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>11</v>
       </c>
@@ -2102,7 +2119,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -2125,7 +2142,7 @@
         <v>9715</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
         <v>14</v>
       </c>
@@ -2148,7 +2165,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>15</v>
       </c>
@@ -2171,7 +2188,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
         <v>16</v>
       </c>
@@ -2194,7 +2211,7 @@
         <v>8852</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>17</v>
       </c>
@@ -2217,7 +2234,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
         <v>18</v>
       </c>
@@ -2240,7 +2257,7 @@
         <v>62248</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
         <v>19</v>
       </c>
@@ -2263,7 +2280,7 @@
         <v>38617</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>20</v>
       </c>
@@ -2286,12 +2303,12 @@
         <v>38</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>21</v>
       </c>
@@ -2314,7 +2331,7 @@
         <v>72892</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>22</v>
       </c>
@@ -2337,7 +2354,7 @@
         <v>123177</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>23</v>
       </c>
@@ -2360,7 +2377,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>24</v>
       </c>
@@ -2383,7 +2400,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
         <v>25</v>
       </c>
@@ -2406,7 +2423,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
         <v>26</v>
       </c>
@@ -2429,7 +2446,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>27</v>
       </c>
@@ -2452,7 +2469,7 @@
         <v>34802</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
         <v>28</v>
       </c>
@@ -2475,7 +2492,7 @@
         <v>34657</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
         <v>33</v>
       </c>
@@ -2498,7 +2515,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>13</v>
       </c>
@@ -2521,7 +2538,7 @@
         <v>10897</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
         <v>14</v>
       </c>
@@ -2544,7 +2561,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
         <v>15</v>
       </c>
@@ -2567,7 +2584,7 @@
         <v>982</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
         <v>16</v>
       </c>
@@ -2590,7 +2607,7 @@
         <v>9575</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>17</v>
       </c>
@@ -2613,7 +2630,7 @@
         <v>3067</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>34</v>
       </c>
@@ -2636,7 +2653,7 @@
         <v>1555</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="6" t="s">
         <v>35</v>
       </c>
@@ -2659,12 +2676,12 @@
         <v>245898</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="6" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>36</v>
       </c>
@@ -2687,7 +2704,7 @@
         <v>7388</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>37</v>
       </c>
@@ -2710,7 +2727,7 @@
         <v>117675</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>38</v>
       </c>
@@ -2733,7 +2750,7 @@
         <v>10352</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>39</v>
       </c>
@@ -2756,7 +2773,7 @@
         <v>73158</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>40</v>
       </c>
@@ -2779,7 +2796,7 @@
         <v>8973</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="6" t="s">
         <v>18</v>
       </c>
@@ -2802,7 +2819,7 @@
         <v>217546</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>41</v>
       </c>
@@ -2825,12 +2842,12 @@
         <v>6.42</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="6" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>42</v>
       </c>
@@ -2853,7 +2870,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>43</v>
       </c>
@@ -2876,7 +2893,7 @@
         <v>3.11</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>44</v>
       </c>
@@ -2899,7 +2916,7 @@
         <v>0.77</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>45</v>
       </c>
@@ -2929,16 +2946,16 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C13558E2-00A1-4977-A88F-59E267D57995}">
-  <dimension ref="A1:I80"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:K80"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.6328125" style="7" customWidth="1"/>
-    <col min="2" max="2" width="41.36328125" customWidth="1"/>
-    <col min="3" max="3" width="12" style="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.6640625" style="7" customWidth="1"/>
+    <col min="2" max="2" width="41.33203125" customWidth="1"/>
+    <col min="3" max="3" width="12" style="17" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
         <v>48</v>
       </c>
@@ -2946,7 +2963,7 @@
         <v>49</v>
       </c>
       <c r="C1" s="15">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D1" s="6">
         <v>2015</v>
@@ -2966,8 +2983,11 @@
       <c r="I1" s="6">
         <v>2020</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="K1" s="6" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="8">
         <v>1000</v>
       </c>
@@ -2997,7 +3017,7 @@
         <v>7388</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="7">
         <v>1100</v>
       </c>
@@ -3006,7 +3026,7 @@
       </c>
       <c r="C3" s="16"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="10">
         <v>1110</v>
       </c>
@@ -3036,7 +3056,7 @@
         <v>1319</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="10">
         <v>1120</v>
       </c>
@@ -3066,7 +3086,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="7">
         <v>1200</v>
       </c>
@@ -3096,7 +3116,7 @@
         <v>2573</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="7">
         <v>1300</v>
       </c>
@@ -3126,7 +3146,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="7">
         <v>1400</v>
       </c>
@@ -3156,7 +3176,7 @@
         <v>2603</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="7">
         <v>1500</v>
       </c>
@@ -3183,7 +3203,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="8">
         <v>2000</v>
       </c>
@@ -3213,7 +3233,7 @@
         <v>118146</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="7">
         <v>2100</v>
       </c>
@@ -3222,7 +3242,7 @@
       </c>
       <c r="C11" s="16"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="10">
         <v>2101</v>
       </c>
@@ -3252,7 +3272,7 @@
         <v>1319</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="10">
         <v>2102</v>
       </c>
@@ -3282,7 +3302,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="10">
         <v>2103</v>
       </c>
@@ -3312,7 +3332,7 @@
         <v>2573</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="10">
         <v>2104</v>
       </c>
@@ -3342,7 +3362,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="10">
         <v>2105</v>
       </c>
@@ -3372,26 +3392,26 @@
         <v>2603</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="7">
         <v>2200</v>
       </c>
-      <c r="B17" s="12" t="s">
+      <c r="B17" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="C17" s="12">
+      <c r="C17" s="20">
         <f>SUM(C18:C40)</f>
         <v>116589.09085071349</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" s="10">
         <v>2201</v>
       </c>
-      <c r="B18" s="9" t="s">
+      <c r="B18" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="C18" s="12">
+      <c r="C18" s="20">
         <f t="shared" ref="C18:C40" si="0">I18/$I$80*$C$80</f>
         <v>17667.596425966785</v>
       </c>
@@ -3413,15 +3433,16 @@
       <c r="I18" s="4">
         <v>13889</v>
       </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J18" s="18"/>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="10">
         <v>2202</v>
       </c>
-      <c r="B19" s="9" t="s">
+      <c r="B19" s="19" t="s">
         <v>67</v>
       </c>
-      <c r="C19" s="12">
+      <c r="C19" s="20">
         <f t="shared" si="0"/>
         <v>4255.0298829907761</v>
       </c>
@@ -3444,14 +3465,14 @@
         <v>3345</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="10">
         <v>2203</v>
       </c>
-      <c r="B20" s="9" t="s">
+      <c r="B20" s="19" t="s">
         <v>68</v>
       </c>
-      <c r="C20" s="12">
+      <c r="C20" s="20">
         <f t="shared" si="0"/>
         <v>241.69078558094094</v>
       </c>
@@ -3474,14 +3495,14 @@
         <v>190</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="10">
         <v>2204</v>
       </c>
-      <c r="B21" s="9" t="s">
+      <c r="B21" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="C21" s="12">
+      <c r="C21" s="20">
         <f t="shared" si="0"/>
         <v>8423.5599058788994</v>
       </c>
@@ -3504,14 +3525,14 @@
         <v>6622</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" s="10">
         <v>2205</v>
       </c>
-      <c r="B22" s="9" t="s">
+      <c r="B22" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="C22" s="12">
+      <c r="C22" s="20">
         <f t="shared" si="0"/>
         <v>4117.6477522395044</v>
       </c>
@@ -3534,14 +3555,14 @@
         <v>3237</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" s="10">
         <v>2206</v>
       </c>
-      <c r="B23" s="9" t="s">
+      <c r="B23" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="C23" s="12">
+      <c r="C23" s="20">
         <f t="shared" si="0"/>
         <v>4509.4412362338717</v>
       </c>
@@ -3564,14 +3585,14 @@
         <v>3545</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" s="10">
         <v>2207</v>
       </c>
-      <c r="B24" s="9" t="s">
+      <c r="B24" s="19" t="s">
         <v>72</v>
       </c>
-      <c r="C24" s="12">
+      <c r="C24" s="20">
         <f t="shared" si="0"/>
         <v>6093.1519101721424</v>
       </c>
@@ -3594,14 +3615,14 @@
         <v>4790</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="10">
         <v>2208</v>
       </c>
-      <c r="B25" s="9" t="s">
+      <c r="B25" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="C25" s="12">
+      <c r="C25" s="20">
         <f t="shared" si="0"/>
         <v>3788.1850497896953</v>
       </c>
@@ -3624,14 +3645,14 @@
         <v>2978</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="10">
         <v>2209</v>
       </c>
-      <c r="B26" s="9" t="s">
+      <c r="B26" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="C26" s="12">
+      <c r="C26" s="20">
         <f t="shared" si="0"/>
         <v>454.12426553892584</v>
       </c>
@@ -3654,14 +3675,14 @@
         <v>357</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="10">
         <v>2210</v>
       </c>
-      <c r="B27" s="9" t="s">
+      <c r="B27" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="C27" s="12">
+      <c r="C27" s="20">
         <f t="shared" si="0"/>
         <v>231.51433145121709</v>
       </c>
@@ -3684,14 +3705,14 @@
         <v>182</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" s="10">
         <v>2211</v>
       </c>
-      <c r="B28" s="9" t="s">
+      <c r="B28" s="19" t="s">
         <v>76</v>
       </c>
-      <c r="C28" s="12">
+      <c r="C28" s="20">
         <f t="shared" si="0"/>
         <v>2823.9660209983626</v>
       </c>
@@ -3714,14 +3735,14 @@
         <v>2220</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" s="10">
         <v>2212</v>
       </c>
-      <c r="B29" s="9" t="s">
+      <c r="B29" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="C29" s="12">
+      <c r="C29" s="20">
         <f t="shared" si="0"/>
         <v>9717.2416371200416</v>
       </c>
@@ -3744,14 +3765,14 @@
         <v>7639</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" s="10">
         <v>2213</v>
       </c>
-      <c r="B30" s="9" t="s">
+      <c r="B30" s="19" t="s">
         <v>78</v>
       </c>
-      <c r="C30" s="12">
+      <c r="C30" s="20">
         <f t="shared" si="0"/>
         <v>14496.358907791593</v>
       </c>
@@ -3774,14 +3795,14 @@
         <v>11396</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" s="10">
         <v>2214</v>
       </c>
-      <c r="B31" s="9" t="s">
+      <c r="B31" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="C31" s="12">
+      <c r="C31" s="20">
         <f t="shared" si="0"/>
         <v>10902.798543232866</v>
       </c>
@@ -3804,14 +3825,14 @@
         <v>8571</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" s="10">
         <v>2215</v>
       </c>
-      <c r="B32" s="9" t="s">
+      <c r="B32" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="C32" s="12">
+      <c r="C32" s="20">
         <f t="shared" si="0"/>
         <v>11009.651311594967</v>
       </c>
@@ -3834,14 +3855,14 @@
         <v>8655</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" s="10">
         <v>2216</v>
       </c>
-      <c r="B33" s="9" t="s">
+      <c r="B33" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="C33" s="12">
+      <c r="C33" s="20">
         <f t="shared" si="0"/>
         <v>2077.2686992298763</v>
       </c>
@@ -3864,14 +3885,14 @@
         <v>1633</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" s="10">
         <v>2217</v>
       </c>
-      <c r="B34" s="9" t="s">
+      <c r="B34" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="C34" s="12">
+      <c r="C34" s="20">
         <f t="shared" si="0"/>
         <v>3325.1563868872609</v>
       </c>
@@ -3894,14 +3915,14 @@
         <v>2614</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" s="10">
         <v>2218</v>
       </c>
-      <c r="B35" s="9" t="s">
+      <c r="B35" s="19" t="s">
         <v>83</v>
       </c>
-      <c r="C35" s="12">
+      <c r="C35" s="20">
         <f t="shared" si="0"/>
         <v>8474.4421765275183</v>
       </c>
@@ -3924,14 +3945,14 @@
         <v>6662</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" s="10">
         <v>2219</v>
       </c>
-      <c r="B36" s="9" t="s">
+      <c r="B36" s="19" t="s">
         <v>84</v>
       </c>
-      <c r="C36" s="12">
+      <c r="C36" s="20">
         <f t="shared" si="0"/>
         <v>1152.4834301912235</v>
       </c>
@@ -3954,14 +3975,14 @@
         <v>906</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" s="10">
         <v>2220</v>
       </c>
-      <c r="B37" s="9" t="s">
+      <c r="B37" s="19" t="s">
         <v>85</v>
       </c>
-      <c r="C37" s="12">
+      <c r="C37" s="20">
         <f t="shared" si="0"/>
         <v>465.57277643486515</v>
       </c>
@@ -3984,14 +4005,14 @@
         <v>366</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" s="10">
         <v>2221</v>
       </c>
-      <c r="B38" s="9" t="s">
+      <c r="B38" s="19" t="s">
         <v>86</v>
       </c>
-      <c r="C38" s="12">
+      <c r="C38" s="20">
         <f t="shared" si="0"/>
         <v>962.94697202511725</v>
       </c>
@@ -4014,14 +4035,14 @@
         <v>757</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" s="10">
         <v>2222</v>
       </c>
-      <c r="B39" s="9" t="s">
+      <c r="B39" s="19" t="s">
         <v>87</v>
       </c>
-      <c r="C39" s="12">
+      <c r="C39" s="20">
         <f t="shared" si="0"/>
         <v>465.57277643486515</v>
       </c>
@@ -4044,15 +4065,15 @@
         <v>366</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" s="10">
         <v>2223</v>
       </c>
-      <c r="B40" s="9" t="s">
+      <c r="B40" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="C40" s="12">
-        <f t="shared" si="0"/>
+      <c r="C40" s="20">
+        <f>I40/$I$80*$C$80</f>
         <v>933.68966640216138</v>
       </c>
       <c r="D40" s="4">
@@ -4074,7 +4095,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" s="7">
         <v>2300</v>
       </c>
@@ -4082,7 +4103,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" s="10">
         <v>2301</v>
       </c>
@@ -4112,7 +4133,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" s="10">
         <v>2302</v>
       </c>
@@ -4142,7 +4163,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" s="10">
         <v>2303</v>
       </c>
@@ -4172,7 +4193,7 @@
         <v>1904</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" s="7">
         <v>2400</v>
       </c>
@@ -4181,7 +4202,7 @@
       </c>
       <c r="C45" s="16"/>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" s="10">
         <v>2410</v>
       </c>
@@ -4211,7 +4232,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" s="10">
         <v>2420</v>
       </c>
@@ -4241,7 +4262,7 @@
         <v>2136</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" s="10">
         <v>2430</v>
       </c>
@@ -4271,7 +4292,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" s="7">
         <v>2500</v>
       </c>
@@ -4301,7 +4322,7 @@
         <v>13476</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" s="8">
         <v>3000</v>
       </c>
@@ -4331,7 +4352,7 @@
         <v>10352</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" s="7">
         <v>3100</v>
       </c>
@@ -4340,7 +4361,7 @@
       </c>
       <c r="C51" s="16"/>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" s="10">
         <v>3101</v>
       </c>
@@ -4370,7 +4391,7 @@
         <v>7375</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" s="10">
         <v>3102</v>
       </c>
@@ -4400,7 +4421,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" s="7">
         <v>3200</v>
       </c>
@@ -4409,7 +4430,7 @@
       </c>
       <c r="C54" s="16"/>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" s="10">
         <v>3210</v>
       </c>
@@ -4439,7 +4460,7 @@
         <v>1771</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" s="10">
         <v>3220</v>
       </c>
@@ -4469,7 +4490,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" s="10">
         <v>3230</v>
       </c>
@@ -4499,7 +4520,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58" s="8">
         <v>4000</v>
       </c>
@@ -4529,7 +4550,7 @@
         <v>73158</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" s="7">
         <v>4100</v>
       </c>
@@ -4559,7 +4580,7 @@
         <v>1924</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" s="7">
         <v>4300</v>
       </c>
@@ -4589,7 +4610,7 @@
         <v>2275</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61" s="7">
         <v>4400</v>
       </c>
@@ -4598,7 +4619,7 @@
       </c>
       <c r="C61" s="16"/>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" s="10">
         <v>4401</v>
       </c>
@@ -4628,7 +4649,7 @@
         <v>50753</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63" s="10">
         <v>4402</v>
       </c>
@@ -4658,7 +4679,7 @@
         <v>18200</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" s="8">
         <v>5000</v>
       </c>
@@ -4688,7 +4709,7 @@
         <v>8973</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65" s="7">
         <v>5100</v>
       </c>
@@ -4697,7 +4718,7 @@
       </c>
       <c r="C65" s="16"/>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A66" s="10">
         <v>5101</v>
       </c>
@@ -4727,7 +4748,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A67" s="10">
         <v>5102</v>
       </c>
@@ -4757,7 +4778,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A68" s="10">
         <v>5103</v>
       </c>
@@ -4787,7 +4808,7 @@
         <v>1335</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A69" s="10">
         <v>5104</v>
       </c>
@@ -4817,7 +4838,7 @@
         <v>1828</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A70" s="7">
         <v>5200</v>
       </c>
@@ -4847,7 +4868,7 @@
         <v>2297</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A71" s="7">
         <v>5300</v>
       </c>
@@ -4856,7 +4877,7 @@
       </c>
       <c r="C71" s="16"/>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A72" s="10">
         <v>5301</v>
       </c>
@@ -4886,7 +4907,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A73" s="10">
         <v>5302</v>
       </c>
@@ -4916,7 +4937,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A74" s="7">
         <v>5400</v>
       </c>
@@ -4925,7 +4946,7 @@
       </c>
       <c r="C74" s="16"/>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A75" s="10">
         <v>5401</v>
       </c>
@@ -4955,7 +4976,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A76" s="10">
         <v>5402</v>
       </c>
@@ -4985,7 +5006,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A77" s="10">
         <v>5403</v>
       </c>
@@ -5015,7 +5036,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A78" s="10">
         <v>5404</v>
       </c>
@@ -5045,7 +5066,7 @@
         <v>1399</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A79" s="10">
         <v>5500</v>
       </c>
@@ -5075,12 +5096,12 @@
         <v>646</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B80" s="8" t="s">
         <v>126</v>
       </c>
       <c r="C80" s="15">
-        <f>[1]yearly_full_release_long_format!$P$335108*1000</f>
+        <f>[1]yearly_full_release_long_format!$I$16*1000</f>
         <v>277330</v>
       </c>
       <c r="D80" s="6">
@@ -5110,12 +5131,12 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB65EAF5-A56E-4270-8472-89080845ECB0}">
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.6328125" customWidth="1"/>
+    <col min="1" max="1" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -5123,7 +5144,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>130</v>
       </c>
@@ -5131,7 +5152,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>131</v>
       </c>
@@ -5139,7 +5160,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>132</v>
       </c>
@@ -5147,7 +5168,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>133</v>
       </c>
@@ -5155,7 +5176,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>134</v>
       </c>
